--- a/site/HR-to-Microsoft-Directory-Integration-Guide/headings.xlsx
+++ b/site/HR-to-Microsoft-Directory-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D41"/>
+  <dimension ref="A1:D45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1167,7 +1167,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Tables</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1189,73 +1189,73 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Basic</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>h_01KQ9Q699N0TNXXRJTKZYM0Z7M</t>
+          <t>h_01KTRP3SFVPGZBZJ6TW8KC7GNS</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-to-Microsoft-Directory-Integration-Guide/#h_01KQ9Q699N0TNXXRJTKZYM0Z7M</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-to-Microsoft-Directory-Integration-Guide/#h_01KTRP3SFVPGZBZJ6TW8KC7GNS</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Integration Execution Report in Excel Format</t>
+          <t>Offboarding</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>h_01K1X7GKQKGYQTTNQVH6GAFV18</t>
+          <t>h_01KTRR9ZW6VPVGBBB44H56WDS1</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-to-Microsoft-Directory-Integration-Guide/#h_01K1X7GKQKGYQTTNQVH6GAFV18</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-to-Microsoft-Directory-Integration-Guide/#h_01KTRR9ZW6VPVGBBB44H56WDS1</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Appendix</t>
+          <t>Tables</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>h_01JACVR5THZC5F22MJPKKAAN97</t>
+          <t>h_01KTRR9ZW6X4WH37EBAANEX40H</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-to-Microsoft-Directory-Integration-Guide/#h_01JACVR5THZC5F22MJPKKAAN97</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-to-Microsoft-Directory-Integration-Guide/#h_01KTRR9ZW6X4WH37EBAANEX40H</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Supported Functions</t>
+          <t>Schedule</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1265,19 +1265,19 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>h_01JKDBS8YHQ5Y7F2PZEEHRFY7P</t>
+          <t>h_01KQ9Q699N0TNXXRJTKZYM0Z7M</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-to-Microsoft-Directory-Integration-Guide/#h_01JKDBS8YHQ5Y7F2PZEEHRFY7P</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-to-Microsoft-Directory-Integration-Guide/#h_01KQ9Q699N0TNXXRJTKZYM0Z7M</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Known Limitations and Issues</t>
+          <t>Integration Execution</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1287,32 +1287,120 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>h_01JKDB4PPPCAQKJQ0BAHDG87GV</t>
+          <t>h_01KWGTB0GVQF47YJNG692DDJJE</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-to-Microsoft-Directory-Integration-Guide/#h_01JKDB4PPPCAQKJQ0BAHDG87GV</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-to-Microsoft-Directory-Integration-Guide/#h_01KWGTB0GVQF47YJNG692DDJJE</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
+          <t>Integration Execution Report in Excel Format</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>h_01K1X7GKQKGYQTTNQVH6GAFV18</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-to-Microsoft-Directory-Integration-Guide/#h_01K1X7GKQKGYQTTNQVH6GAFV18</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Appendix</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>h_01JACVR5THZC5F22MJPKKAAN97</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-to-Microsoft-Directory-Integration-Guide/#h_01JACVR5THZC5F22MJPKKAAN97</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Supported Functions</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>h_01JKDBS8YHQ5Y7F2PZEEHRFY7P</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-to-Microsoft-Directory-Integration-Guide/#h_01JKDBS8YHQ5Y7F2PZEEHRFY7P</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Known Limitations and Issues</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>h_01JKDB4PPPCAQKJQ0BAHDG87GV</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-to-Microsoft-Directory-Integration-Guide/#h_01JKDB4PPPCAQKJQ0BAHDG87GV</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
           <t>References</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C45" t="inlineStr">
         <is>
           <t>h_01K592V1HARY29EJ5PN39KB4F9</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D45" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-to-Microsoft-Directory-Integration-Guide/#h_01K592V1HARY29EJ5PN39KB4F9</t>
         </is>

--- a/site/HR-to-Microsoft-Directory-Integration-Guide/headings.xlsx
+++ b/site/HR-to-Microsoft-Directory-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D45"/>
+  <dimension ref="A1:D49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1167,7 +1167,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>Writeback</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1177,12 +1177,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>h_01JV4VH803XE82ZDJ9EMERFAXE</t>
+          <t>h_01KXJ4J3ANKKT3JZTNY97SZ39P</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-to-Microsoft-Directory-Integration-Guide/#h_01JV4VH803XE82ZDJ9EMERFAXE</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-to-Microsoft-Directory-Integration-Guide/#h_01KXJ4J3ANKKT3JZTNY97SZ39P</t>
         </is>
       </c>
     </row>
@@ -1199,19 +1199,19 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>h_01KTRP3SFVPGZBZJ6TW8KC7GNS</t>
+          <t>h_01KYHK6HW10A336RAHCBZHHX4P</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-to-Microsoft-Directory-Integration-Guide/#h_01KTRP3SFVPGZBZJ6TW8KC7GNS</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-to-Microsoft-Directory-Integration-Guide/#h_01KYHK6HW10A336RAHCBZHHX4P</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Offboarding</t>
+          <t>Attribute Map</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1221,41 +1221,41 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>h_01KTRR9ZW6VPVGBBB44H56WDS1</t>
+          <t>h_01KXJB70WVXPF13YB3DJ9DHY9F</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-to-Microsoft-Directory-Integration-Guide/#h_01KTRR9ZW6VPVGBBB44H56WDS1</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-to-Microsoft-Directory-Integration-Guide/#h_01KXJB70WVXPF13YB3DJ9DHY9F</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Tables</t>
+          <t>Preview Employee Data</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>h_01KTRR9ZW6X4WH37EBAANEX40H</t>
+          <t>h_01KXJB70WV47G9BH5Y2MQ59DD9</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-to-Microsoft-Directory-Integration-Guide/#h_01KTRR9ZW6X4WH37EBAANEX40H</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-to-Microsoft-Directory-Integration-Guide/#h_01KXJB70WV47G9BH5Y2MQ59DD9</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1265,85 +1265,85 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>h_01KQ9Q699N0TNXXRJTKZYM0Z7M</t>
+          <t>h_01JV4VH803XE82ZDJ9EMERFAXE</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-to-Microsoft-Directory-Integration-Guide/#h_01KQ9Q699N0TNXXRJTKZYM0Z7M</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-to-Microsoft-Directory-Integration-Guide/#h_01JV4VH803XE82ZDJ9EMERFAXE</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Integration Execution</t>
+          <t>Basic</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>h_01KWGTB0GVQF47YJNG692DDJJE</t>
+          <t>h_01KTRP3SFVPGZBZJ6TW8KC7GNS</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-to-Microsoft-Directory-Integration-Guide/#h_01KWGTB0GVQF47YJNG692DDJJE</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-to-Microsoft-Directory-Integration-Guide/#h_01KTRP3SFVPGZBZJ6TW8KC7GNS</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Integration Execution Report in Excel Format</t>
+          <t>Offboarding</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>h_01K1X7GKQKGYQTTNQVH6GAFV18</t>
+          <t>h_01KTRR9ZW6VPVGBBB44H56WDS1</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-to-Microsoft-Directory-Integration-Guide/#h_01K1X7GKQKGYQTTNQVH6GAFV18</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-to-Microsoft-Directory-Integration-Guide/#h_01KTRR9ZW6VPVGBBB44H56WDS1</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Appendix</t>
+          <t>Tables</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>h_01JACVR5THZC5F22MJPKKAAN97</t>
+          <t>h_01KTRR9ZW6X4WH37EBAANEX40H</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-to-Microsoft-Directory-Integration-Guide/#h_01JACVR5THZC5F22MJPKKAAN97</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-to-Microsoft-Directory-Integration-Guide/#h_01KTRR9ZW6X4WH37EBAANEX40H</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Supported Functions</t>
+          <t>Schedule</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1353,19 +1353,19 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>h_01JKDBS8YHQ5Y7F2PZEEHRFY7P</t>
+          <t>h_01KQ9Q699N0TNXXRJTKZYM0Z7M</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-to-Microsoft-Directory-Integration-Guide/#h_01JKDBS8YHQ5Y7F2PZEEHRFY7P</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-to-Microsoft-Directory-Integration-Guide/#h_01KQ9Q699N0TNXXRJTKZYM0Z7M</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Known Limitations and Issues</t>
+          <t>Integration Execution</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1375,32 +1375,120 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>h_01JKDB4PPPCAQKJQ0BAHDG87GV</t>
+          <t>h_01KWGTB0GVQF47YJNG692DDJJE</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-to-Microsoft-Directory-Integration-Guide/#h_01JKDB4PPPCAQKJQ0BAHDG87GV</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-to-Microsoft-Directory-Integration-Guide/#h_01KWGTB0GVQF47YJNG692DDJJE</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
+          <t>Integration Execution Report in Excel Format</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>h_01K1X7GKQKGYQTTNQVH6GAFV18</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-to-Microsoft-Directory-Integration-Guide/#h_01K1X7GKQKGYQTTNQVH6GAFV18</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Appendix</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>h_01JACVR5THZC5F22MJPKKAAN97</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-to-Microsoft-Directory-Integration-Guide/#h_01JACVR5THZC5F22MJPKKAAN97</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Supported Functions</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>h_01JKDBS8YHQ5Y7F2PZEEHRFY7P</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-to-Microsoft-Directory-Integration-Guide/#h_01JKDBS8YHQ5Y7F2PZEEHRFY7P</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Known Limitations and Issues</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>h_01JKDB4PPPCAQKJQ0BAHDG87GV</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-to-Microsoft-Directory-Integration-Guide/#h_01JKDB4PPPCAQKJQ0BAHDG87GV</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
           <t>References</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B49" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>h_01K592V1HARY29EJ5PN39KB4F9</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="D49" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-to-Microsoft-Directory-Integration-Guide/#h_01K592V1HARY29EJ5PN39KB4F9</t>
         </is>
